--- a/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
@@ -565,10 +565,10 @@
         <v>0.05</v>
       </c>
       <c r="G11" t="n">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="H11" t="n">
-        <v>5.75</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="12">
@@ -591,10 +591,10 @@
         <v>6</v>
       </c>
       <c r="G12" t="n">
-        <v>0.18</v>
+        <v>0.105</v>
       </c>
       <c r="H12" t="n">
-        <v>1.08</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>29.71</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="14">
@@ -750,7 +750,7 @@
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>34.31</v>
+        <v>33.51</v>
       </c>
       <c r="H22" t="n">
         <v>0.34</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="5" t="n">
-        <v>34.65</v>
+        <v>33.85</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H23"/>
+  <dimension ref="A3:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -574,7 +574,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MT-MOR-PEGA</t>
+          <t>MT-CEMENTO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -584,192 +584,244 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Mortero de pega para mampostería, elaborado con cemento y arena lavada.</t>
+          <t>Cemento Portland gris tipo I, en saco. Para mortero de pega.</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>2.04</v>
       </c>
       <c r="G12" t="n">
-        <v>0.105</v>
+        <v>0.225</v>
       </c>
       <c r="H12" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="13">
-      <c r="F13" s="1" t="inlineStr">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MT-ARENA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Arena lavada de río, puesta en obra, para camas de asiento y rellenos de zanja. Para mortero de pega.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.0063</v>
+      </c>
+      <c r="G13" t="n">
+        <v>22</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MT-AGUA-OBRA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>m3</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Agua para amasado, humectación de rellenos y compactación. Para mortero de pega.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.0012</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="F15" s="1" t="inlineStr">
         <is>
           <t>Subtotal materiales:</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>28.91</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
+      <c r="H15" t="n">
+        <v>28.88</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="1" t="inlineStr">
+      <c r="E16" s="1" t="inlineStr">
         <is>
           <t>Equipo y maquinaria</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>MQ-MEZCL</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Mezcladora de concreto y mortero de 1 saco, incluida amortización y combustible.</t>
         </is>
       </c>
-      <c r="F15" t="n">
+      <c r="F17" t="n">
         <v>0.04</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G17" t="n">
         <v>3.6</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H17" t="n">
         <v>0.14</v>
       </c>
     </row>
-    <row r="16">
-      <c r="F16" s="1" t="inlineStr">
+    <row r="18">
+      <c r="F18" s="1" t="inlineStr">
         <is>
           <t>Subtotal equipo y maquinaria:</t>
         </is>
       </c>
-      <c r="H16" t="n">
+      <c r="H18" t="n">
         <v>0.14</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="19">
+      <c r="A19" t="n">
         <v>3</v>
       </c>
-      <c r="E17" s="1" t="inlineStr">
+      <c r="E19" s="1" t="inlineStr">
         <is>
           <t>Mano de obra</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>MO-OF1-ALB</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Oficial de 1ª albañil.</t>
         </is>
       </c>
-      <c r="F18" t="n">
+      <c r="F20" t="n">
         <v>0.48</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G20" t="n">
         <v>5.5</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H20" t="n">
         <v>2.64</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>MO-AYU</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Ayudante.</t>
         </is>
       </c>
-      <c r="F19" t="n">
+      <c r="F21" t="n">
         <v>0.52</v>
       </c>
-      <c r="G19" t="n">
+      <c r="G21" t="n">
         <v>3.5</v>
       </c>
-      <c r="H19" t="n">
+      <c r="H21" t="n">
         <v>1.82</v>
       </c>
     </row>
-    <row r="20">
-      <c r="F20" s="1" t="inlineStr">
+    <row r="22">
+      <c r="F22" s="1" t="inlineStr">
         <is>
           <t>Subtotal mano de obra:</t>
         </is>
       </c>
-      <c r="H20" t="n">
+      <c r="H22" t="n">
         <v>4.46</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="23">
+      <c r="A23" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="1" t="inlineStr">
+      <c r="E23" s="1" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="D22" t="inlineStr">
+    <row r="24">
+      <c r="D24" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>Costes directos complementarios</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>33.51</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="G24" t="n">
+        <v>33.48</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Costes directos (1+2+3+4):</t>
         </is>
       </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="5" t="n">
-        <v>33.85</v>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="5" t="n">
+        <v>33.81</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-18-02-030.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 18 Obras exteriores y urbanismo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Brocales, aceras y drenajes</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
